--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104464_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104464_W1.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6606</v>
+        <v>5.2352</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5418</v>
+        <v>3.9355</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1188</v>
+        <v>1.2997</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5796</v>
+        <v>4.579</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7733</v>
+        <v>0.7808</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8063</v>
+        <v>3.7982</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6267</v>
+        <v>4.6047</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L2" t="n">
-        <v>3.7263</v>
+        <v>3.7083</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0471</v>
+        <v>-0.0257</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4653</v>
+        <v>-0.8885</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0434</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4219</v>
+        <v>-0.268</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4058</v>
+        <v>3.6041</v>
       </c>
       <c r="E3" t="n">
-        <v>2.53</v>
+        <v>1.7599</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8758</v>
+        <v>1.8442</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7109</v>
+        <v>1.7178</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7778</v>
+        <v>0.7729</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9449</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9312</v>
+        <v>1.9159</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7073</v>
+        <v>1.6925</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2203</v>
+        <v>-0.1981</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7091</v>
+        <v>0.7215</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>1.041</v>
+        <v>0.223</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5989</v>
+        <v>-0.156</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4422</v>
+        <v>0.379</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5626</v>
+        <v>2.9023</v>
       </c>
       <c r="E4" t="n">
-        <v>1.83</v>
+        <v>2.2954</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7327</v>
+        <v>0.6068</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0187</v>
+        <v>-0.0256</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.73</v>
+        <v>-1.7372</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7113</v>
+        <v>1.7116</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2806</v>
+        <v>2.2516</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6274</v>
+        <v>-0.6452</v>
       </c>
       <c r="L4" t="n">
-        <v>2.908</v>
+        <v>2.8968</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2993</v>
+        <v>-2.2772</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0862</v>
+        <v>0.4239</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4506</v>
+        <v>0.0439</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.3801</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5416</v>
+        <v>1.6987</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1275</v>
+        <v>0.4715</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4142</v>
+        <v>1.2272</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2116</v>
+        <v>-0.2166</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.3707</v>
+        <v>-2.375</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1591</v>
+        <v>2.1584</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0185</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4413</v>
+        <v>-1.4554</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4499</v>
+        <v>1.4369</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2203</v>
+        <v>-0.1981</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7091</v>
+        <v>0.7215</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2882</v>
+        <v>-0.1334</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9739</v>
+        <v>-0.5995</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6856</v>
+        <v>0.4661</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5407999999999999</v>
+        <v>1.082</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4136</v>
+        <v>-0.8467</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9544</v>
+        <v>1.9287</v>
       </c>
       <c r="G6" t="n">
-        <v>2.255</v>
+        <v>2.2522</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1573</v>
+        <v>-0.1579</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4123</v>
+        <v>2.4101</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5521</v>
+        <v>3.5253</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9453</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6068</v>
+        <v>2.5912</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2971</v>
+        <v>-1.2731</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2172</v>
+        <v>0.3322</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5898</v>
+        <v>0.0229</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3726</v>
+        <v>0.3093</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3218</v>
+        <v>0.2109</v>
       </c>
       <c r="E7" t="n">
-        <v>0.242</v>
+        <v>-0.0919</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0798</v>
+        <v>0.3027</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4766</v>
+        <v>-1.3894</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8528</v>
+        <v>-0.8707</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6238</v>
+        <v>-0.5187</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5323</v>
+        <v>-0.1728</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3912</v>
+        <v>-0.4104</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1411</v>
+        <v>0.2377</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0089</v>
+        <v>-1.2166</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.244</v>
+        <v>-0.4603</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>2.252</v>
+        <v>0.2345</v>
       </c>
       <c r="T7" t="n">
-        <v>1.978</v>
+        <v>0.0809</v>
       </c>
       <c r="U7" t="n">
-        <v>0.274</v>
+        <v>0.1535</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>G. GRINVALDS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1936</v>
+        <v>-0.2812</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0948</v>
+        <v>-0.7016</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0988</v>
+        <v>0.4204</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3907</v>
+        <v>-0.4738</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8789</v>
+        <v>0.1579</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5118</v>
+        <v>-0.6317</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1523</v>
+        <v>-0.7896</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4054</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2531</v>
+        <v>-0.7896</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2384</v>
+        <v>0.3159</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4735</v>
+        <v>0.1579</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7649</v>
+        <v>0.1579</v>
       </c>
       <c r="P8" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1639</v>
+        <v>0.0349</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0575</v>
+        <v>-0.0697</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2214</v>
+        <v>0.1046</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. GRINVALDS</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3389</v>
+        <v>-0.6931</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6952</v>
+        <v>-0.9208</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3563</v>
+        <v>0.2277</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4718</v>
+        <v>-0.4022</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1573</v>
+        <v>-0.1146</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6291</v>
+        <v>-0.2876</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7864</v>
+        <v>0.3133</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.2003</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7864</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3145</v>
+        <v>-0.7155</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1573</v>
+        <v>0.0857</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1573</v>
+        <v>-0.8012</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0278</v>
+        <v>-0.6551</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0696</v>
+        <v>-0.4601</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0417</v>
+        <v>-0.195</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>-0.7739</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>-0.7739</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0463</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1345</v>
+        <v>-1.0621</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0882</v>
+        <v>0.2289</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3948</v>
+        <v>-1.4834</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1096</v>
+        <v>-0.853</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2852</v>
+        <v>-0.6304</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3324</v>
+        <v>0.5084</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1874</v>
+        <v>0.3825</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.1259</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7272</v>
+        <v>-1.9918</v>
       </c>
       <c r="N10" t="n">
-        <v>0.07779999999999999</v>
+        <v>-1.2355</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.805</v>
+        <v>-0.7563</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0144</v>
+        <v>1.1055</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6956</v>
+        <v>0.7058</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3188</v>
+        <v>0.3997</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2194</v>
+        <v>-0.9349</v>
       </c>
       <c r="E11" t="n">
-        <v>0.521</v>
+        <v>0.88</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7404</v>
+        <v>-1.8149</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4126</v>
+        <v>0.4102</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7245</v>
+        <v>0.7184</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3118</v>
+        <v>-0.3082</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8275</v>
+        <v>1.8139</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1185</v>
+        <v>1.1064</v>
       </c>
       <c r="L11" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4149</v>
+        <v>-1.4037</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4606</v>
+        <v>0.7444</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1724</v>
+        <v>0.2042</v>
       </c>
       <c r="U11" t="n">
-        <v>0.633</v>
+        <v>0.5402</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3563</v>
+        <v>-1.0685</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1523</v>
+        <v>-2.7593</v>
       </c>
       <c r="F12" t="n">
-        <v>1.796</v>
+        <v>1.6908</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3754</v>
+        <v>-0.3765</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.124</v>
+        <v>-2.1253</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7486</v>
+        <v>1.7488</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9333</v>
+        <v>-0.952</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.0127</v>
+        <v>-2.0242</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5578</v>
+        <v>0.5755</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7126</v>
+        <v>-0.4158</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0434</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3309</v>
+        <v>0.2047</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.6404</v>
+        <v>-1.6436</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5949</v>
+        <v>-0.4857</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0455</v>
+        <v>-1.1579</v>
       </c>
       <c r="G13" t="n">
-        <v>0.62</v>
+        <v>0.6249</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1269</v>
+        <v>0.1318</v>
       </c>
       <c r="I13" t="n">
         <v>0.4931</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.7247</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L13" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1063</v>
+        <v>-0.0998</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5553</v>
+        <v>-0.5644</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3478</v>
+        <v>-0.2301</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2075</v>
+        <v>-0.3344</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.238299999999999</v>
+        <v>9.278700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.706999999999999</v>
+        <v>2.474199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>6.531499999999999</v>
+        <v>6.8043</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2385</v>
+        <v>5.2166</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.6635</v>
+        <v>-5.6719</v>
       </c>
       <c r="I14" t="n">
-        <v>10.902</v>
+        <v>10.8885</v>
       </c>
       <c r="J14" t="n">
-        <v>13.9458</v>
+        <v>13.7249</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4059000000000003</v>
+        <v>0.2933999999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>13.5399</v>
+        <v>13.4314</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.707499999999998</v>
+        <v>-8.5082</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.0693</v>
+        <v>-5.965499999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.6382</v>
+        <v>-2.542899999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>4.536799999999999</v>
+        <v>4.552699999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.4759</v>
+        <v>-12.5198</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0125</v>
+        <v>17.0724</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6049000000000003</v>
+        <v>0.4411999999999998</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.7521</v>
+        <v>-1.6987</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1472</v>
+        <v>2.1398</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9319000000000002</v>
+        <v>-0.9316000000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>2.989</v>
+        <v>2.968</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.9209</v>
+        <v>-3.8995</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7552</v>
+        <v>3.0817</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1681</v>
+        <v>3.0264</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4129</v>
+        <v>0.0553</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2181</v>
+        <v>2.2199</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7574</v>
+        <v>0.7664</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4607</v>
+        <v>1.4536</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1238</v>
+        <v>2.1021</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2233</v>
+        <v>1.2058</v>
       </c>
       <c r="M15" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1178</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0835</v>
+        <v>0.4065</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0484</v>
+        <v>-0.1652</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1318</v>
+        <v>0.5718</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>I. WONG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5685</v>
+        <v>0.8017</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2306</v>
+        <v>-0.5614</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6621</v>
+        <v>1.3632</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0726</v>
+        <v>0.8336</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7865</v>
+        <v>1.7465</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7139</v>
+        <v>-0.913</v>
       </c>
       <c r="J16" t="n">
-        <v>2.956</v>
+        <v>1.5186</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7246</v>
+        <v>1.6752</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2315</v>
+        <v>-0.1566</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8834</v>
+        <v>-0.6851</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.9453</v>
+        <v>-0.7563</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5205</v>
+        <v>-0.1637</v>
       </c>
       <c r="T16" t="n">
-        <v>0.248</v>
+        <v>-0.2998</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2725</v>
+        <v>0.1361</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9320000000000001</v>
+        <v>2.4082</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>1.6342</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. WONG</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2573</v>
+        <v>0.73</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6429</v>
+        <v>1.1786</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9002</v>
+        <v>-0.4486</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8349</v>
+        <v>-0.3964</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7518</v>
+        <v>-0.0806</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9169</v>
+        <v>-0.3159</v>
       </c>
       <c r="J17" t="n">
-        <v>1.538</v>
+        <v>2.7096</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6899</v>
+        <v>0.1929</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.152</v>
+        <v>2.5168</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.703</v>
+        <v>-3.1061</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0619</v>
+        <v>-0.2734</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7649</v>
+        <v>-2.8326</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.2683</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7195</v>
+        <v>0.2159</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4174</v>
+        <v>-0.3929</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3021</v>
+        <v>0.6088</v>
       </c>
       <c r="V17" t="n">
-        <v>2.4102</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0081</v>
+        <v>0.6287</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1972</v>
+        <v>0.1349</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1891</v>
+        <v>0.4938</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.335</v>
+        <v>-1.3388</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2802</v>
+        <v>0.2651</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6152</v>
+        <v>-1.6038</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0479</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1598</v>
+        <v>-0.1798</v>
       </c>
       <c r="L18" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2871</v>
+        <v>-1.2706</v>
       </c>
       <c r="N18" t="n">
-        <v>0.44</v>
+        <v>0.4449</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3536</v>
+        <v>0.2845</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6956</v>
+        <v>-0.3417</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3421</v>
+        <v>0.6262</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. MANIEMA</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0159</v>
+        <v>0.1904</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1573</v>
+        <v>1.8533</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1732</v>
+        <v>-1.6629</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1732</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1732</v>
+        <v>1.781</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1.7052</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2.9385</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.7097</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.2288</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1732</v>
+        <v>-2.8628</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1732</v>
+        <v>0.0713</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-2.934</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1573</v>
+        <v>0.1359</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1573</v>
+        <v>-0.1048</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.2407</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.9317</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>L. MANIEMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0696</v>
+        <v>0.104</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6145</v>
+        <v>0.2764</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5449000000000001</v>
+        <v>-0.1724</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7162</v>
+        <v>-0.1724</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3218</v>
+        <v>-0.1724</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3945</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3743</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1185</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2558</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3419</v>
+        <v>-0.1724</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2033</v>
+        <v>-0.1724</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1387</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.9488</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.2764</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1603</v>
+        <v>0.2764</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2507</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0698</v>
+        <v>-0.0443</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8516</v>
+        <v>-0.8901</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9215</v>
+        <v>0.8457</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3983</v>
+        <v>1.7128</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0837</v>
+        <v>1.3212</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3145</v>
+        <v>0.3916</v>
       </c>
       <c r="J21" t="n">
-        <v>2.7328</v>
+        <v>1.3517</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2007</v>
+        <v>1.1064</v>
       </c>
       <c r="L21" t="n">
-        <v>2.5321</v>
+        <v>0.2453</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.1311</v>
+        <v>0.3611</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2844</v>
+        <v>0.2148</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.8467</v>
+        <v>0.1463</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9073</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5789</v>
+        <v>-0.0452</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.747</v>
+        <v>-0.0746</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1681</v>
+        <v>0.0294</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. ANGOLA</t>
+          <t>M. SALVO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4672</v>
+        <v>-1.5914</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0359</v>
+        <v>-2.9257</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.503</v>
+        <v>1.3343</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2178</v>
+        <v>-2.2756</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4776</v>
+        <v>0.0806</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6954</v>
+        <v>-2.3562</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6952</v>
+        <v>-1.3064</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4475</v>
+        <v>-0.6657</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2477</v>
+        <v>-0.6407</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.913</v>
+        <v>-0.9692</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0301</v>
+        <v>0.7463</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9431</v>
+        <v>-1.7155</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>1.7091</v>
+        <v>0.4566</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2461</v>
+        <v>-0.4811</v>
       </c>
       <c r="U22" t="n">
-        <v>0.463</v>
+        <v>0.9377</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SALVO</t>
+          <t>B. ANGOLA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2943</v>
+        <v>-1.6427</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2609</v>
+        <v>-0.3051</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9667</v>
+        <v>-1.3376</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.2805</v>
+        <v>-0.2313</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0837</v>
+        <v>1.4763</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.3643</v>
+        <v>-1.7076</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.292</v>
+        <v>1.6562</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6549</v>
+        <v>1.4339</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6371</v>
+        <v>0.2223</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9885</v>
+        <v>-1.8876</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7387</v>
+        <v>0.0424</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7272</v>
+        <v>-1.93</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7594</v>
+        <v>0.54</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8347</v>
+        <v>-0.0492</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5942</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.874</v>
+        <v>-3.6889</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1214</v>
+        <v>-3.783</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2475</v>
+        <v>0.0941</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.6777</v>
+        <v>-2.6579</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3296</v>
+        <v>-2.3266</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1756</v>
+        <v>-1.1835</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1732</v>
+        <v>0.1724</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3488</v>
+        <v>-1.3559</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.502</v>
+        <v>-1.4744</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1282</v>
+        <v>0.0373</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6775</v>
+        <v>-0.3232</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5492</v>
+        <v>0.3605</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="25">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.0204</v>
+        <v>-5.2231</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.138</v>
+        <v>-4.8087</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8825</v>
+        <v>-0.4144</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.9978</v>
+        <v>-2.9863</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.1906</v>
+        <v>-1.181</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.8072</v>
+        <v>-1.8053</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.1971</v>
+        <v>-1.2105</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3708</v>
+        <v>-0.376</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.8264</v>
+        <v>-0.8345</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.8007</v>
+        <v>-1.7758</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7543</v>
+        <v>0.0395</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5383</v>
+        <v>-0.1838</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.216</v>
+        <v>0.2232</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.238300000000001</v>
+        <v>-6.6539</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.5314</v>
+        <v>-6.804399999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.7068</v>
+        <v>0.1504999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.2385</v>
+        <v>-5.2166</v>
       </c>
       <c r="H26" t="n">
-        <v>5.6635</v>
+        <v>5.6719</v>
       </c>
       <c r="I26" t="n">
-        <v>-10.9018</v>
+        <v>-10.8884</v>
       </c>
       <c r="J26" t="n">
-        <v>8.7075</v>
+        <v>8.508199999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>6.069399999999999</v>
+        <v>5.9653</v>
       </c>
       <c r="L26" t="n">
-        <v>2.6381</v>
+        <v>2.542999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-13.9458</v>
+        <v>-13.7251</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4057999999999999</v>
+        <v>-0.2934</v>
       </c>
       <c r="O26" t="n">
-        <v>-13.54</v>
+        <v>-13.4315</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.5366</v>
+        <v>-4.5526</v>
       </c>
       <c r="Q26" t="n">
-        <v>-17.0126</v>
+        <v>-17.0726</v>
       </c>
       <c r="R26" t="n">
-        <v>12.476</v>
+        <v>12.52</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6048999999999998</v>
+        <v>2.1837</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.1472</v>
+        <v>-2.1399</v>
       </c>
       <c r="U26" t="n">
-        <v>2.7521</v>
+        <v>4.3236</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9319000000000004</v>
+        <v>0.9316999999999998</v>
       </c>
       <c r="W26" t="n">
-        <v>3.9209</v>
+        <v>3.8995</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.989</v>
+        <v>-2.9679</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104464_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104464_W1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-3.8995</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104464_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-2.9679</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
